--- a/converted/tozalangan/baliqchi/Sentabr 10 kunlik/Elektr Transformatorlar.xlsx
+++ b/converted/tozalangan/baliqchi/Sentabr 10 kunlik/Elektr Transformatorlar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="219">
   <si>
     <t>Transformatorlar Sentabr (1–10) Holatiga Ko'ra</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Ma'sul xodim (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
@@ -401,6 +404,9 @@
   </si>
   <si>
     <t>40.79775104, 40.79775104</t>
+  </si>
+  <si>
+    <t>Koordinata Andijon viloyatidan tashqarida yoki to'liq emas - bo'sh qoldirildi</t>
   </si>
   <si>
     <t>baliqchi/Sentabr 10 kunlik/Elektr Transformatorlar.xlsx, 47-qator</t>
@@ -1083,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V86"/>
+  <dimension ref="A1:W86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
@@ -1094,10 +1100,10 @@
     <col min="12" max="12" width="18" style="1" customWidth="1"/>
     <col min="13" max="14" width="14" style="4" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>
-    <col min="16" max="22" width="26" customWidth="1"/>
+    <col min="16" max="23" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1122,8 +1128,9 @@
       <c r="T1"/>
       <c r="U1"/>
       <c r="V1"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W1"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1190,16 +1197,19 @@
       <c r="V2" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W2" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1">
         <v>7402.8</v>
@@ -1217,7 +1227,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="3">
         <v>40.81609</v>
@@ -1229,24 +1239,24 @@
         <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
-      </c>
-      <c r="V3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1">
         <v>2393.2000000000003</v>
@@ -1264,7 +1274,7 @@
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J4" s="3">
         <v>40.90925541</v>
@@ -1276,24 +1286,24 @@
         <v>160</v>
       </c>
       <c r="O4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="s">
-        <v>28</v>
-      </c>
-      <c r="V4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1">
         <v>2280.5</v>
@@ -1311,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J5" s="3">
         <v>40.88711767</v>
@@ -1323,24 +1333,24 @@
         <v>63</v>
       </c>
       <c r="O5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="s">
-        <v>28</v>
-      </c>
-      <c r="V5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1">
         <v>344.91</v>
@@ -1358,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6" s="3">
         <v>40.88711767</v>
@@ -1370,24 +1380,24 @@
         <v>630</v>
       </c>
       <c r="O6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="s">
-        <v>28</v>
-      </c>
-      <c r="V6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1">
         <v>3288</v>
@@ -1405,7 +1415,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7" s="3">
         <v>40.8157433333</v>
@@ -1417,27 +1427,27 @@
         <v>250</v>
       </c>
       <c r="O7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R7" t="s">
-        <v>38</v>
-      </c>
-      <c r="V7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1">
         <v>2715.6</v>
@@ -1455,7 +1465,7 @@
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3">
         <v>40.8157433333</v>
@@ -1467,24 +1477,24 @@
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="s">
-        <v>28</v>
-      </c>
-      <c r="V8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1">
         <v>9439.5</v>
@@ -1502,7 +1512,7 @@
         <v>3</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9" s="3">
         <v>40.80106297</v>
@@ -1514,27 +1524,27 @@
         <v>160</v>
       </c>
       <c r="O9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R9" t="s">
-        <v>44</v>
-      </c>
-      <c r="V9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1">
         <v>1426</v>
@@ -1552,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J10" s="3">
         <v>40.8290266667</v>
@@ -1564,27 +1574,27 @@
         <v>63</v>
       </c>
       <c r="O10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R10" t="s">
-        <v>47</v>
-      </c>
-      <c r="V10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1">
         <v>12294.6</v>
@@ -1602,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J11" s="3">
         <v>40.830398658</v>
@@ -1614,24 +1624,24 @@
         <v>250</v>
       </c>
       <c r="O11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q11" t="s">
-        <v>28</v>
-      </c>
-      <c r="V11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1">
         <v>6609.2</v>
@@ -1649,7 +1659,7 @@
         <v>10</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J12" s="3">
         <v>40.8157433333</v>
@@ -1661,24 +1671,24 @@
         <v>160</v>
       </c>
       <c r="O12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="s">
-        <v>28</v>
-      </c>
-      <c r="V12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1">
         <v>5115</v>
@@ -1696,7 +1706,7 @@
         <v>3</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J13" s="3">
         <v>40.81793038</v>
@@ -1708,24 +1718,24 @@
         <v>160</v>
       </c>
       <c r="O13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>28</v>
-      </c>
-      <c r="V13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="1">
         <v>5022</v>
@@ -1743,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J14" s="3">
         <v>40.8290366667</v>
@@ -1755,24 +1765,24 @@
         <v>160</v>
       </c>
       <c r="O14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q14" t="s">
-        <v>28</v>
-      </c>
-      <c r="V14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1">
         <v>6305.400000000001</v>
@@ -1790,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J15" s="3">
         <v>40.8294633333</v>
@@ -1802,24 +1812,24 @@
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q15" t="s">
-        <v>28</v>
-      </c>
-      <c r="V15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1">
         <v>3596</v>
@@ -1837,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J16" s="3">
         <v>40.80232555</v>
@@ -1849,24 +1859,24 @@
         <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q16" t="s">
-        <v>28</v>
-      </c>
-      <c r="V16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="1">
         <v>18860.399999999998</v>
@@ -1884,7 +1894,7 @@
         <v>24</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J17" s="3">
         <v>40.81005246</v>
@@ -1896,24 +1906,24 @@
         <v>250</v>
       </c>
       <c r="O17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q17" t="s">
-        <v>28</v>
-      </c>
-      <c r="V17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" s="1">
         <v>16603.600000000002</v>
@@ -1931,7 +1941,7 @@
         <v>8</v>
       </c>
       <c r="I18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J18" s="3">
         <v>40.8334316667</v>
@@ -1943,24 +1953,24 @@
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q18" t="s">
-        <v>28</v>
-      </c>
-      <c r="V18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" s="1">
         <v>10248.6</v>
@@ -1978,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J19" s="3">
         <v>40.833005</v>
@@ -1990,24 +2000,24 @@
         <v>100</v>
       </c>
       <c r="O19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
-      </c>
-      <c r="V19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" s="1">
         <v>13671</v>
@@ -2025,7 +2035,7 @@
         <v>8</v>
       </c>
       <c r="I20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J20" s="3">
         <v>40.8286033333</v>
@@ -2037,24 +2047,24 @@
         <v>160</v>
       </c>
       <c r="O20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q20" t="s">
-        <v>28</v>
-      </c>
-      <c r="V20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D21" s="1">
         <v>48156</v>
@@ -2072,7 +2082,7 @@
         <v>13</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J21" s="3">
         <v>40.81609088</v>
@@ -2084,24 +2094,24 @@
         <v>250</v>
       </c>
       <c r="O21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q21" t="s">
-        <v>28</v>
-      </c>
-      <c r="V21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="W21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D22" s="1">
         <v>5620.3</v>
@@ -2119,7 +2129,7 @@
         <v>8</v>
       </c>
       <c r="I22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J22" s="3">
         <v>40.79375079</v>
@@ -2131,30 +2141,30 @@
         <v>180</v>
       </c>
       <c r="O22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U22" t="s">
-        <v>76</v>
-      </c>
-      <c r="V22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D23" s="1">
         <v>35005.200000000004</v>
@@ -2172,7 +2182,7 @@
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J23" s="3">
         <v>40.7991896931</v>
@@ -2184,30 +2194,30 @@
         <v>160</v>
       </c>
       <c r="O23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U23" t="s">
-        <v>76</v>
-      </c>
-      <c r="V23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D24" s="1">
         <v>28030.2</v>
@@ -2225,7 +2235,7 @@
         <v>5</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J24" s="3">
         <v>40.78871505</v>
@@ -2237,30 +2247,30 @@
         <v>160</v>
       </c>
       <c r="O24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U24" t="s">
-        <v>76</v>
-      </c>
-      <c r="V24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D25" s="1">
         <v>26821.2</v>
@@ -2278,7 +2288,7 @@
         <v>6</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J25" s="3">
         <v>40.79409543</v>
@@ -2290,30 +2300,30 @@
         <v>160</v>
       </c>
       <c r="O25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U25" t="s">
-        <v>76</v>
-      </c>
-      <c r="V25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D26" s="1">
         <v>12173.699999999999</v>
@@ -2331,7 +2341,7 @@
         <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J26" s="3">
         <v>40.79310688</v>
@@ -2343,33 +2353,33 @@
         <v>160</v>
       </c>
       <c r="O26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U26" t="s">
-        <v>76</v>
-      </c>
-      <c r="V26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D27" s="1">
         <v>14284.800000000001</v>
@@ -2387,7 +2397,7 @@
         <v>6</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J27" s="3">
         <v>40.78598722</v>
@@ -2399,30 +2409,30 @@
         <v>160</v>
       </c>
       <c r="O27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U27" t="s">
-        <v>76</v>
-      </c>
-      <c r="V27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D28" s="1">
         <v>16855</v>
@@ -2440,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J28" s="3">
         <v>40.78768601</v>
@@ -2452,30 +2462,30 @@
         <v>100</v>
       </c>
       <c r="O28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U28" t="s">
-        <v>76</v>
-      </c>
-      <c r="V28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D29" s="1">
         <v>3763.4</v>
@@ -2493,7 +2503,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J29" s="3">
         <v>40.78719516</v>
@@ -2505,30 +2515,30 @@
         <v>63</v>
       </c>
       <c r="O29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U29" t="s">
-        <v>76</v>
-      </c>
-      <c r="V29" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D30" s="1">
         <v>8956</v>
@@ -2546,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J30" s="3">
         <v>40.7991896931</v>
@@ -2558,33 +2568,33 @@
         <v>250</v>
       </c>
       <c r="O30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U30" t="s">
-        <v>76</v>
-      </c>
-      <c r="V30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D31" s="1">
         <v>2046</v>
@@ -2602,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J31" s="3">
         <v>40.7991896931</v>
@@ -2614,33 +2624,33 @@
         <v>250</v>
       </c>
       <c r="O31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U31" t="s">
-        <v>76</v>
-      </c>
-      <c r="V31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D32" s="1">
         <v>12688</v>
@@ -2658,7 +2668,7 @@
         <v>3</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J32" s="3">
         <v>40.78580216</v>
@@ -2670,30 +2680,30 @@
         <v>250</v>
       </c>
       <c r="O32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U32" t="s">
-        <v>76</v>
-      </c>
-      <c r="V32" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D33" s="1">
         <v>7117.599999999999</v>
@@ -2711,7 +2721,7 @@
         <v>2</v>
       </c>
       <c r="I33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J33" s="3">
         <v>40.79602292</v>
@@ -2723,30 +2733,30 @@
         <v>100</v>
       </c>
       <c r="O33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U33" t="s">
-        <v>76</v>
-      </c>
-      <c r="V33" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W33" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34" s="1">
         <v>14182.5</v>
@@ -2764,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J34" s="3">
         <v>40.79788315</v>
@@ -2776,30 +2786,30 @@
         <v>100</v>
       </c>
       <c r="O34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U34" t="s">
-        <v>76</v>
-      </c>
-      <c r="V34" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D35" s="1">
         <v>10695</v>
@@ -2817,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J35" s="3">
         <v>40.7991896931</v>
@@ -2829,30 +2839,30 @@
         <v>160</v>
       </c>
       <c r="O35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U35" t="s">
-        <v>76</v>
-      </c>
-      <c r="V35" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D36" s="1">
         <v>8295.6</v>
@@ -2870,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J36" s="3">
         <v>40.79775104</v>
@@ -2882,30 +2892,30 @@
         <v>160</v>
       </c>
       <c r="O36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U36" t="s">
-        <v>76</v>
-      </c>
-      <c r="V36" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D37" s="1">
         <v>4147.8</v>
@@ -2923,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J37" s="3">
         <v>40.90925541</v>
@@ -2935,30 +2945,30 @@
         <v>100</v>
       </c>
       <c r="O37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U37" t="s">
-        <v>76</v>
-      </c>
-      <c r="V37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D38" s="1">
         <v>7948.4</v>
@@ -2976,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J38" s="3">
         <v>40.7991896931</v>
@@ -2988,30 +2998,30 @@
         <v>250</v>
       </c>
       <c r="O38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U38" t="s">
-        <v>76</v>
-      </c>
-      <c r="V38" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D39" s="1">
         <v>12040.4</v>
@@ -3029,7 +3039,7 @@
         <v>2</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J39" s="3">
         <v>40.79775104</v>
@@ -3041,30 +3051,30 @@
         <v>160</v>
       </c>
       <c r="O39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q39" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U39" t="s">
-        <v>76</v>
-      </c>
-      <c r="V39" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D40" s="1">
         <v>3392</v>
@@ -3082,7 +3092,7 @@
         <v>3</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J40" s="3">
         <v>40.79090901</v>
@@ -3094,30 +3104,30 @@
         <v>160</v>
       </c>
       <c r="O40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U40" t="s">
-        <v>76</v>
-      </c>
-      <c r="V40" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D41" s="1">
         <v>1821</v>
@@ -3144,30 +3154,30 @@
         <v>160</v>
       </c>
       <c r="O41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U41" t="s">
-        <v>76</v>
-      </c>
-      <c r="V41" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D42" s="1">
         <v>13892</v>
@@ -3185,7 +3195,7 @@
         <v>3</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J42" s="3">
         <v>40.7985166667</v>
@@ -3197,30 +3207,30 @@
         <v>160</v>
       </c>
       <c r="O42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U42" t="s">
-        <v>76</v>
-      </c>
-      <c r="V42" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W42" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D43" s="1">
         <v>10931</v>
@@ -3247,30 +3257,30 @@
         <v>63</v>
       </c>
       <c r="O43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P43" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U43" t="s">
-        <v>76</v>
-      </c>
-      <c r="V43" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W43" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D44" s="1">
         <v>3608.4</v>
@@ -3297,30 +3307,30 @@
         <v>160</v>
       </c>
       <c r="O44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P44" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q44" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U44" t="s">
-        <v>76</v>
-      </c>
-      <c r="V44" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D45" s="1">
         <v>2249.6</v>
@@ -3347,30 +3357,30 @@
         <v>40</v>
       </c>
       <c r="O45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U45" t="s">
-        <v>76</v>
-      </c>
-      <c r="V45" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D46" s="1">
         <v>2564.7</v>
@@ -3397,30 +3407,30 @@
         <v>40</v>
       </c>
       <c r="O46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P46" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U46" t="s">
-        <v>76</v>
-      </c>
-      <c r="V46" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D47" s="1">
         <v>1956</v>
@@ -3441,33 +3451,36 @@
         <v>100</v>
       </c>
       <c r="O47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T47" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V47" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="W47" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D48" s="1">
         <v>2372</v>
@@ -3485,7 +3498,7 @@
         <v>6</v>
       </c>
       <c r="I48" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J48" s="3">
         <v>40.7962902775</v>
@@ -3497,33 +3510,33 @@
         <v>100</v>
       </c>
       <c r="O48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U48" t="s">
-        <v>76</v>
-      </c>
-      <c r="V48" t="s">
+        <v>77</v>
+      </c>
+      <c r="W48" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>23</v>
-      </c>
-      <c r="B49" t="s">
-        <v>131</v>
-      </c>
       <c r="C49" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D49" s="1">
         <v>2207.2000000000003</v>
@@ -3541,7 +3554,7 @@
         <v>3</v>
       </c>
       <c r="I49" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J49" s="3">
         <v>40.818536561</v>
@@ -3553,30 +3566,30 @@
         <v>100</v>
       </c>
       <c r="O49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U49" t="s">
-        <v>76</v>
-      </c>
-      <c r="V49" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D50" s="1">
         <v>3521.6</v>
@@ -3594,7 +3607,7 @@
         <v>2</v>
       </c>
       <c r="I50" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J50" s="3">
         <v>40.81459547</v>
@@ -3606,30 +3619,30 @@
         <v>100</v>
       </c>
       <c r="O50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U50" t="s">
-        <v>76</v>
-      </c>
-      <c r="V50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W50" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D51" s="1">
         <v>26511.2</v>
@@ -3647,7 +3660,7 @@
         <v>2</v>
       </c>
       <c r="I51" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J51" s="3">
         <v>40.8008333333</v>
@@ -3659,30 +3672,30 @@
         <v>250</v>
       </c>
       <c r="O51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P51" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q51" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U51" t="s">
-        <v>76</v>
-      </c>
-      <c r="V51" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W51" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D52" s="1">
         <v>7402.8</v>
@@ -3700,7 +3713,7 @@
         <v>5</v>
       </c>
       <c r="I52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J52" s="3">
         <v>40.8040866667</v>
@@ -3712,30 +3725,30 @@
         <v>160</v>
       </c>
       <c r="O52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U52" t="s">
-        <v>76</v>
-      </c>
-      <c r="V52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D53" s="1">
         <v>20236.8</v>
@@ -3753,7 +3766,7 @@
         <v>6</v>
       </c>
       <c r="I53" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J53" s="3">
         <v>40.8006516667</v>
@@ -3765,30 +3778,30 @@
         <v>250</v>
       </c>
       <c r="O53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U53" t="s">
-        <v>76</v>
-      </c>
-      <c r="V53" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W53" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C54" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D54" s="1">
         <v>9656</v>
@@ -3806,7 +3819,7 @@
         <v>9</v>
       </c>
       <c r="I54" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J54" s="3">
         <v>40.813765</v>
@@ -3818,30 +3831,30 @@
         <v>100</v>
       </c>
       <c r="O54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P54" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q54" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U54" t="s">
-        <v>76</v>
-      </c>
-      <c r="V54" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W54" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C55" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D55" s="1">
         <v>4566</v>
@@ -3859,7 +3872,7 @@
         <v>5</v>
       </c>
       <c r="I55" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J55" s="3">
         <v>40.8974016667</v>
@@ -3871,30 +3884,30 @@
         <v>63</v>
       </c>
       <c r="O55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U55" t="s">
-        <v>76</v>
-      </c>
-      <c r="V55" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W55" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D56" s="1">
         <v>2126.6</v>
@@ -3912,7 +3925,7 @@
         <v>3</v>
       </c>
       <c r="I56" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J56" s="3">
         <v>40.8124399418</v>
@@ -3924,30 +3937,30 @@
         <v>63</v>
       </c>
       <c r="O56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U56" t="s">
-        <v>76</v>
-      </c>
-      <c r="V56" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W56" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B57" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C57" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D57" s="1">
         <v>8425.800000000001</v>
@@ -3965,7 +3978,7 @@
         <v>2</v>
       </c>
       <c r="I57" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J57" s="3">
         <v>40.8011416667</v>
@@ -3977,33 +3990,33 @@
         <v>63</v>
       </c>
       <c r="O57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S57" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U57" t="s">
-        <v>76</v>
-      </c>
-      <c r="V57" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C58" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D58" s="1">
         <v>3806.7999999999997</v>
@@ -4021,7 +4034,7 @@
         <v>4</v>
       </c>
       <c r="I58" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J58" s="3">
         <v>40.8191205282</v>
@@ -4033,30 +4046,30 @@
         <v>100</v>
       </c>
       <c r="O58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P58" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q58" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U58" t="s">
-        <v>76</v>
-      </c>
-      <c r="V58" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W58" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D59" s="1">
         <v>5487</v>
@@ -4074,7 +4087,7 @@
         <v>4</v>
       </c>
       <c r="I59" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J59" s="3">
         <v>40.8372428315</v>
@@ -4086,30 +4099,30 @@
         <v>63</v>
       </c>
       <c r="O59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P59" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q59" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U59" t="s">
-        <v>76</v>
-      </c>
-      <c r="V59" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C60" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D60" s="1">
         <v>1432.2</v>
@@ -4136,30 +4149,30 @@
         <v>63</v>
       </c>
       <c r="O60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P60" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q60" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U60" t="s">
-        <v>76</v>
-      </c>
-      <c r="V60" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W60" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D61" s="1">
         <v>1153.2</v>
@@ -4186,30 +4199,30 @@
         <v>100</v>
       </c>
       <c r="O61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U61" t="s">
-        <v>76</v>
-      </c>
-      <c r="V61" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W61" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C62" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D62" s="1">
         <v>9089.199999999999</v>
@@ -4227,7 +4240,7 @@
         <v>5</v>
       </c>
       <c r="I62" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J62" s="3">
         <v>40.8309649536</v>
@@ -4239,30 +4252,30 @@
         <v>100</v>
       </c>
       <c r="O62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P62" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q62" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U62" t="s">
-        <v>76</v>
-      </c>
-      <c r="V62" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W62" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D63" s="1">
         <v>9473.6</v>
@@ -4280,39 +4293,42 @@
         <v>12</v>
       </c>
       <c r="I63" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L63" s="1">
         <v>250</v>
       </c>
       <c r="O63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P63" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q63" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T63" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="U63" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V63" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="W63" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D64" s="1">
         <v>6246.5</v>
@@ -4339,30 +4355,30 @@
         <v>100</v>
       </c>
       <c r="O64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P64" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q64" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U64" t="s">
-        <v>76</v>
-      </c>
-      <c r="V64" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D65" s="1">
         <v>5487</v>
@@ -4389,30 +4405,30 @@
         <v>100</v>
       </c>
       <c r="O65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P65" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q65" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U65" t="s">
-        <v>76</v>
-      </c>
-      <c r="V65" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C66" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D66" s="1">
         <v>8101</v>
@@ -4430,7 +4446,7 @@
         <v>6</v>
       </c>
       <c r="I66" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J66" s="3">
         <v>40.7988133333</v>
@@ -4442,30 +4458,30 @@
         <v>100</v>
       </c>
       <c r="O66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P66" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q66" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U66" t="s">
-        <v>76</v>
-      </c>
-      <c r="V66" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C67" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D67" s="1">
         <v>2653.6</v>
@@ -4492,30 +4508,30 @@
         <v>100</v>
       </c>
       <c r="O67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P67" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q67" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U67" t="s">
-        <v>76</v>
-      </c>
-      <c r="V67" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W67" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B68" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C68" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D68" s="1">
         <v>13546</v>
@@ -4533,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J68" s="3">
         <v>40.8049033333</v>
@@ -4545,30 +4561,30 @@
         <v>160</v>
       </c>
       <c r="O68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U68" t="s">
-        <v>76</v>
-      </c>
-      <c r="V68" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C69" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D69" s="1">
         <v>7502</v>
@@ -4595,30 +4611,30 @@
         <v>400</v>
       </c>
       <c r="O69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P69" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q69" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U69" t="s">
-        <v>76</v>
-      </c>
-      <c r="V69" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W69" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C70" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D70" s="1">
         <v>744</v>
@@ -4645,30 +4661,30 @@
         <v>63</v>
       </c>
       <c r="O70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P70" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q70" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U70" t="s">
-        <v>76</v>
-      </c>
-      <c r="V70" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W70" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B71" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C71" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D71" s="1">
         <v>12437.199999999999</v>
@@ -4686,7 +4702,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J71" s="3">
         <v>40.7953283333</v>
@@ -4698,30 +4714,30 @@
         <v>100</v>
       </c>
       <c r="O71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U71" t="s">
-        <v>76</v>
-      </c>
-      <c r="V71" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W71" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B72" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C72" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D72" s="1">
         <v>11801.699999999999</v>
@@ -4739,7 +4755,7 @@
         <v>6</v>
       </c>
       <c r="I72" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J72" s="3">
         <v>40.8158216667</v>
@@ -4751,30 +4767,30 @@
         <v>100</v>
       </c>
       <c r="O72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P72" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q72" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U72" t="s">
-        <v>76</v>
-      </c>
-      <c r="V72" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W72" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B73" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C73" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D73" s="1">
         <v>24759.7</v>
@@ -4792,7 +4808,7 @@
         <v>5</v>
       </c>
       <c r="I73" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J73" s="3">
         <v>40.80361</v>
@@ -4804,30 +4820,30 @@
         <v>250</v>
       </c>
       <c r="O73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U73" t="s">
-        <v>76</v>
-      </c>
-      <c r="V73" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W73" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C74" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D74" s="1">
         <v>1962.3</v>
@@ -4845,7 +4861,7 @@
         <v>3</v>
       </c>
       <c r="I74" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J74" s="3">
         <v>40.84186131</v>
@@ -4857,30 +4873,30 @@
         <v>100</v>
       </c>
       <c r="O74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U74" t="s">
-        <v>76</v>
-      </c>
-      <c r="V74" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W74" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C75" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D75" s="1">
         <v>4491.900000000001</v>
@@ -4898,7 +4914,7 @@
         <v>2</v>
       </c>
       <c r="I75" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J75" s="3">
         <v>40.83796068</v>
@@ -4910,30 +4926,30 @@
         <v>63</v>
       </c>
       <c r="O75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P75" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q75" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U75" t="s">
-        <v>76</v>
-      </c>
-      <c r="V75" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W75" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C76" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D76" s="1">
         <v>1822.8</v>
@@ -4951,7 +4967,7 @@
         <v>2</v>
       </c>
       <c r="I76" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J76" s="3">
         <v>40.798545</v>
@@ -4963,33 +4979,33 @@
         <v>160</v>
       </c>
       <c r="O76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P76" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q76" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R76" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="U76" t="s">
-        <v>76</v>
-      </c>
-      <c r="V76" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W76" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C77" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D77" s="1">
         <v>1875.5</v>
@@ -5007,7 +5023,7 @@
         <v>2</v>
       </c>
       <c r="I77" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J77" s="3">
         <v>40.8364763064</v>
@@ -5019,30 +5035,30 @@
         <v>160</v>
       </c>
       <c r="O77" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U77" t="s">
-        <v>76</v>
-      </c>
-      <c r="V77" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W77" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B78" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C78" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D78" s="1">
         <v>2802.4</v>
@@ -5060,7 +5076,7 @@
         <v>4</v>
       </c>
       <c r="I78" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J78" s="3">
         <v>40.8141511492</v>
@@ -5072,33 +5088,33 @@
         <v>160</v>
       </c>
       <c r="O78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P78" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q78" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S78" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U78" t="s">
-        <v>76</v>
-      </c>
-      <c r="V78" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W78" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B79" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D79" s="1">
         <v>2027.4</v>
@@ -5116,7 +5132,7 @@
         <v>3</v>
       </c>
       <c r="I79" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J79" s="3">
         <v>40.8161615906</v>
@@ -5128,30 +5144,30 @@
         <v>40</v>
       </c>
       <c r="O79" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P79" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q79" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U79" t="s">
-        <v>76</v>
-      </c>
-      <c r="V79" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W79" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B80" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C80" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D80" s="1">
         <v>11305.699999999999</v>
@@ -5169,7 +5185,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J80" s="3">
         <v>40.7949233333</v>
@@ -5181,30 +5197,30 @@
         <v>160</v>
       </c>
       <c r="O80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P80" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q80" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U80" t="s">
-        <v>76</v>
-      </c>
-      <c r="V80" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B81" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D81" s="1">
         <v>3236.4</v>
@@ -5222,39 +5238,42 @@
         <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L81" s="1">
         <v>160</v>
       </c>
       <c r="O81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P81" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q81" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T81" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="U81" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V81" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="W81" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B82" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C82" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D82" s="1">
         <v>644</v>
@@ -5272,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J82" s="3">
         <v>40.7989133333</v>
@@ -5284,30 +5303,30 @@
         <v>63</v>
       </c>
       <c r="O82" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P82" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q82" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U82" t="s">
-        <v>76</v>
-      </c>
-      <c r="V82" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B83" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C83" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D83" s="1">
         <v>1822.8</v>
@@ -5334,30 +5353,30 @@
         <v>160</v>
       </c>
       <c r="O83" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P83" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q83" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U83" t="s">
-        <v>76</v>
-      </c>
-      <c r="V83" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B84" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C84" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D84" s="1">
         <v>4017.6</v>
@@ -5384,30 +5403,30 @@
         <v>160</v>
       </c>
       <c r="O84" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P84" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q84" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U84" t="s">
-        <v>76</v>
-      </c>
-      <c r="V84" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B85" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C85" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D85" s="1">
         <v>1729.8</v>
@@ -5434,30 +5453,30 @@
         <v>100</v>
       </c>
       <c r="O85" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P85" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q85" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U85" t="s">
-        <v>76</v>
-      </c>
-      <c r="V85" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B86" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C86" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D86" s="1">
         <v>9374.4</v>
@@ -5478,27 +5497,30 @@
         <v>100</v>
       </c>
       <c r="O86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P86" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q86" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T86" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="U86" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V86" t="s">
-        <v>216</v>
+        <v>131</v>
+      </c>
+      <c r="W86" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
